--- a/pdd-initiation-coverage/PDD_Financial_Model_2026-05-25.xlsx
+++ b/pdd-initiation-coverage/PDD_Financial_Model_2026-05-25.xlsx
@@ -14,6 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資產負債表" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情境分析" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF輸入" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF分析" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敏感度分析" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可比公司分析" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值摘要" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +26,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;–&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;–&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;0.00"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="171" formatCode="0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +88,75 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F497D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +179,41 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,6 +372,93 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -928,6 +1125,1225 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>PDD Holdings — 可比公司分析（截至2026年5月25日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
+          <t>代碼</t>
+        </is>
+      </c>
+      <c r="C3" s="71" t="inlineStr">
+        <is>
+          <t>市值（$B）</t>
+        </is>
+      </c>
+      <c r="D3" s="71" t="inlineStr">
+        <is>
+          <t>EV（$B）</t>
+        </is>
+      </c>
+      <c r="E3" s="71" t="inlineStr">
+        <is>
+          <t>EV/Rev LTM</t>
+        </is>
+      </c>
+      <c r="F3" s="71" t="inlineStr">
+        <is>
+          <t>EV/Rev NTM</t>
+        </is>
+      </c>
+      <c r="G3" s="71" t="inlineStr">
+        <is>
+          <t>EV/EBITDA LTM</t>
+        </is>
+      </c>
+      <c r="H3" s="71" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM</t>
+        </is>
+      </c>
+      <c r="I3" s="71" t="inlineStr">
+        <is>
+          <t>P/E NTM</t>
+        </is>
+      </c>
+      <c r="J3" s="71" t="inlineStr">
+        <is>
+          <t>收入增長%</t>
+        </is>
+      </c>
+      <c r="K3" s="71" t="inlineStr">
+        <is>
+          <t>EBITDA率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>阿里巴巴</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="C4" s="72" t="n">
+        <v>270</v>
+      </c>
+      <c r="D4" s="72" t="n">
+        <v>210</v>
+      </c>
+      <c r="E4" s="73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="73" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G4" s="73" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="H4" s="73" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I4" s="74" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" s="75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K4" s="75" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>京東</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="n">
+        <v>65</v>
+      </c>
+      <c r="D5" s="72" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="73" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H5" s="73" t="n">
+        <v>32</v>
+      </c>
+      <c r="I5" s="74" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" s="75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K5" s="75" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>亞馬遜</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D6" s="72" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E6" s="73" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" s="73" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G6" s="73" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="H6" s="73" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I6" s="74" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" s="75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K6" s="75" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="n">
+        <v>83</v>
+      </c>
+      <c r="D7" s="72" t="n">
+        <v>85</v>
+      </c>
+      <c r="E7" s="73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F7" s="73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G7" s="73" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="H7" s="73" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I7" s="74" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7" s="75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K7" s="75" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>海洋集團</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="72" t="n">
+        <v>47</v>
+      </c>
+      <c r="E8" s="73" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F8" s="73" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G8" s="73" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="H8" s="73" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I8" s="74" t="n">
+        <v>35</v>
+      </c>
+      <c r="J8" s="75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K8" s="75" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="n">
+        <v>130</v>
+      </c>
+      <c r="D9" s="72" t="n">
+        <v>128</v>
+      </c>
+      <c r="E9" s="73" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F9" s="73" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="73" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="H9" s="73" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I9" s="74" t="n">
+        <v>55</v>
+      </c>
+      <c r="J9" s="75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K9" s="75" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>酷澎</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="n">
+        <v>38</v>
+      </c>
+      <c r="D10" s="72" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" s="73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F10" s="73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>n.m.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>n.m.</t>
+        </is>
+      </c>
+      <c r="I10" s="74" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" s="75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K10" s="75" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>統計摘要（排除 JD 及 CPNG 在 EV/EBITDA 上的異常值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>統計</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr"/>
+      <c r="C13" s="58" t="inlineStr"/>
+      <c r="D13" s="58" t="inlineStr"/>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>EV/Rev LTM</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>EV/Rev NTM</t>
+        </is>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>EV/EBITDA LTM</t>
+        </is>
+      </c>
+      <c r="H13" s="58" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM</t>
+        </is>
+      </c>
+      <c r="I13" s="58" t="inlineStr">
+        <is>
+          <t>P/E NTM</t>
+        </is>
+      </c>
+      <c r="J13" s="58" t="inlineStr">
+        <is>
+          <t>收入增長%</t>
+        </is>
+      </c>
+      <c r="K13" s="58" t="inlineStr">
+        <is>
+          <t>EBITDA率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>最大值</t>
+        </is>
+      </c>
+      <c r="E14" s="73" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F14" s="73" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="73" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="H14" s="73" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I14" s="74" t="n">
+        <v>55</v>
+      </c>
+      <c r="J14" s="75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K14" s="75" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>75 百分位</t>
+        </is>
+      </c>
+      <c r="E15" s="73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F15" s="73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G15" s="73" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="H15" s="73" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I15" s="74" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" s="75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K15" s="75" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>中位數</t>
+        </is>
+      </c>
+      <c r="E16" s="73" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F16" s="73" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G16" s="73" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="H16" s="73" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I16" s="74" t="n">
+        <v>35</v>
+      </c>
+      <c r="J16" s="75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K16" s="75" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>25 百分位</t>
+        </is>
+      </c>
+      <c r="E17" s="73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F17" s="73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G17" s="73" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="H17" s="73" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I17" s="74" t="n">
+        <v>14</v>
+      </c>
+      <c r="J17" s="75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K17" s="75" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>最小值</t>
+        </is>
+      </c>
+      <c r="E18" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="73" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="H18" s="73" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I18" s="74" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" s="75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K18" s="75" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>▶ PDD 當前市場隱含倍數（2026年5月25日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="76" t="inlineStr">
+        <is>
+          <t>PDD Holdings</t>
+        </is>
+      </c>
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>PDD</t>
+        </is>
+      </c>
+      <c r="C21" s="77" t="n">
+        <v>149</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>89</v>
+      </c>
+      <c r="E21" s="78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F21" s="78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G21" s="78" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H21" s="78" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I21" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="80" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="K21" s="80" t="n">
+        <v>0.297</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>PDD 可比公司法隱含估值（8x NTM EV/EBITDA，中國ADR折讓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>PDD 2026E EBITDA（美元）</t>
+        </is>
+      </c>
+      <c r="C24" s="81" t="inlineStr">
+        <is>
+          <t>$25.8B</t>
+        </is>
+      </c>
+      <c r="E24" s="82" t="inlineStr">
+        <is>
+          <t>¥185,400M ÷ 7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>應用倍數（中國ADR折讓 8x）</t>
+        </is>
+      </c>
+      <c r="C25" s="81" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="E25" s="82" t="inlineStr">
+        <is>
+          <t>BABA為11.2x，PDD因Temu風險給予折讓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>隱含企業價值</t>
+        </is>
+      </c>
+      <c r="C26" s="81" t="inlineStr">
+        <is>
+          <t>$206B</t>
+        </is>
+      </c>
+      <c r="E26" s="82">
+        <f> $25.8B × 8x</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>加：淨現金</t>
+        </is>
+      </c>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
+          <t>$60.1B</t>
+        </is>
+      </c>
+      <c r="E27" s="82" t="inlineStr">
+        <is>
+          <t>截至2024A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>股權價值</t>
+        </is>
+      </c>
+      <c r="C28" s="81" t="inlineStr">
+        <is>
+          <t>$266B</t>
+        </is>
+      </c>
+      <c r="E28" s="82" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>稀釋後 ADS</t>
+        </is>
+      </c>
+      <c r="C29" s="81" t="inlineStr">
+        <is>
+          <t>1,450M</t>
+        </is>
+      </c>
+      <c r="E29" s="82" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>每 ADS 隱含股價</t>
+        </is>
+      </c>
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>$184</t>
+        </is>
+      </c>
+      <c r="E30" s="82" t="inlineStr">
+        <is>
+          <t>可比公司法目標股價</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>較現價上行空間</t>
+        </is>
+      </c>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>+79%</t>
+        </is>
+      </c>
+      <c r="E31" s="82" t="inlineStr">
+        <is>
+          <t>現價 $103</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A20:K20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>PDD Holdings — 估值摘要 &amp; 投資建議</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="83" t="inlineStr">
+        <is>
+          <t>投資評級：★★★ 買入（BUY）/ 超配（Outperform）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>目標股價（12個月）</t>
+        </is>
+      </c>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>$165 /ADS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>加權估值，保守調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>當前股價</t>
+        </is>
+      </c>
+      <c r="B6" s="84" t="inlineStr">
+        <is>
+          <t>$103 /ADS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026年5月25日</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>上行空間</t>
+        </is>
+      </c>
+      <c r="B7" s="84" t="inlineStr">
+        <is>
+          <t>+60.2%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>市值</t>
+        </is>
+      </c>
+      <c r="B8" s="84" t="inlineStr">
+        <is>
+          <t>$149B</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1,450M 稀釋後 ADS × $103</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>淨現金</t>
+        </is>
+      </c>
+      <c r="B9" s="84" t="inlineStr">
+        <is>
+          <t>$60.1B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>現金 + 短投 − 負債</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>企業價值</t>
+        </is>
+      </c>
+      <c r="B10" s="84" t="inlineStr">
+        <is>
+          <t>$89B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>市值 − 淨現金</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>2026E EV/EBITDA（當前）</t>
+        </is>
+      </c>
+      <c r="B11" s="84" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>¥185,400M EBITDA ÷ $89B EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>2025E NTM P/E（Non-GAAP）</t>
+        </is>
+      </c>
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>7.0x</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>$103 ÷ $14.7 EPS est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="inlineStr">
+        <is>
+          <t>估值足球場（每 ADS 美元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>估值方法</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="inlineStr">
+        <is>
+          <t>低值</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="inlineStr">
+        <is>
+          <t>基本值</t>
+        </is>
+      </c>
+      <c r="D16" s="71" t="inlineStr">
+        <is>
+          <t>高值</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>加權比例</t>
+        </is>
+      </c>
+      <c r="F16" s="71" t="inlineStr">
+        <is>
+          <t>加權貢獻</t>
+        </is>
+      </c>
+      <c r="G16" s="71" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DCF（悲觀/基本加權）</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="n">
+        <v>204</v>
+      </c>
+      <c r="C17" s="72" t="n">
+        <v>243</v>
+      </c>
+      <c r="D17" s="85" t="n">
+        <v>269</v>
+      </c>
+      <c r="E17" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="72" t="n">
+        <v>97</v>
+      </c>
+      <c r="G17" s="87" t="inlineStr">
+        <is>
+          <t>WACC=11.5−14%，g=2−3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>可比公司—中國ADR折讓</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="n">
+        <v>166</v>
+      </c>
+      <c r="C18" s="72" t="n">
+        <v>184</v>
+      </c>
+      <c r="D18" s="65" t="n">
+        <v>219</v>
+      </c>
+      <c r="E18" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="72" t="n">
+        <v>74</v>
+      </c>
+      <c r="G18" s="87" t="inlineStr">
+        <is>
+          <t>7−10x NTM EV/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>可比公司—全球中位數</t>
+        </is>
+      </c>
+      <c r="B19" s="66" t="n">
+        <v>287</v>
+      </c>
+      <c r="C19" s="72" t="n">
+        <v>312</v>
+      </c>
+      <c r="D19" s="66" t="n">
+        <v>341</v>
+      </c>
+      <c r="E19" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="72" t="n">
+        <v>62</v>
+      </c>
+      <c r="G19" s="87" t="inlineStr">
+        <is>
+          <t>13.8−16.9x NTM EV/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>加權平均目標股價</t>
+        </is>
+      </c>
+      <c r="F20" s="88" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>12個月目標股價（保守調整）</t>
+        </is>
+      </c>
+      <c r="B21" s="89" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>上行空間</t>
+        </is>
+      </c>
+      <c r="B22" s="90" t="n">
+        <v>0.6019417475728155</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="52" t="inlineStr">
+        <is>
+          <t>情境分析（概率加權）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t>情境</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>概率</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>核心假設</t>
+        </is>
+      </c>
+      <c r="D26" s="58" t="inlineStr">
+        <is>
+          <t>DCF 每ADS</t>
+        </is>
+      </c>
+      <c r="E26" s="58" t="inlineStr">
+        <is>
+          <t>可比公司每ADS</t>
+        </is>
+      </c>
+      <c r="F26" s="58" t="inlineStr">
+        <is>
+          <t>加權目標</t>
+        </is>
+      </c>
+      <c r="G26" s="58" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>悲觀情境</t>
+        </is>
+      </c>
+      <c r="B27" s="91" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Temu美國收入−30%，EBITDA率27%，WACC=14%</t>
+        </is>
+      </c>
+      <c r="D27" s="72" t="n">
+        <v>204</v>
+      </c>
+      <c r="E27" s="72" t="n">
+        <v>110</v>
+      </c>
+      <c r="F27" s="92" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>基本情境</t>
+        </is>
+      </c>
+      <c r="B28" s="91" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Temu平穩復甦，EBITDA率34%，WACC=11.5%</t>
+        </is>
+      </c>
+      <c r="D28" s="72" t="n">
+        <v>269</v>
+      </c>
+      <c r="E28" s="72" t="n">
+        <v>184</v>
+      </c>
+      <c r="F28" s="66" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>樂觀情境</t>
+        </is>
+      </c>
+      <c r="B29" s="91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Temu加速，ADR折讓縮減，EBITDA率38%，WACC=10%</t>
+        </is>
+      </c>
+      <c r="D29" s="72" t="n">
+        <v>338</v>
+      </c>
+      <c r="E29" s="72" t="n">
+        <v>250</v>
+      </c>
+      <c r="F29" s="65" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>概率加權期望值</t>
+        </is>
+      </c>
+      <c r="B30" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="F30" s="93" t="n">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8523,4 +9939,1251 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>PDD Holdings — 現金流折現法（DCF）估值</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>WACC 計算假設</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>輸入項目</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr"/>
+      <c r="D4" s="53" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="E4" s="53" t="inlineStr"/>
+      <c r="F4" s="53" t="inlineStr"/>
+      <c r="G4" s="53" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  無風險利率（美國10年期國債）</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026年5月市場利率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  公司 Beta（中國 ADR 加成）</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>高波動性，VIE 溢價</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  股票風險溢價（ERP）</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Damodaran 全球 ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  中國 ADR 國家風險溢價</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VIE + 政治風險</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  股權成本 Ke（CAPM + 國家溢價）</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D9">
+        <f> 4.4% + 1.45×5.5% + 1.5%</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  稅前債務成本 Kd</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>境外融資參考利率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  有效稅率</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HNTE + 海南自貿港</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  稅後債務成本</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D12">
+        <f> 5.5% × (1−14%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  資本結構（債務比例）</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>淨現金為正，視同100%股權</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  基本情境 WACC</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>模型建議區間10%–11.5%上緣</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>企業價值 → 股權價值橋接（美元十億）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>企業價值（EV）</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>330.1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>美元十億</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>¥2,376,784M ÷ USD/CNY 7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>加：淨現金（現金+短投−負債）</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>美元十億</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>截至2024A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="53">
+        <f> 股權價值</f>
+        <v/>
+      </c>
+      <c r="B19" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>美元十億</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>稀釋後 ADS（百萬）</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FY2024 稀釋後</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>每 ADS 公允價值（美元）</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="n">
+        <v>269</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>$/ADS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>基本情境 WACC=11.5%, g=3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>當前股價（美元）</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>103</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>$/ADS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026年5月25日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>上行空間</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D23">
+        <f>($269−$103)/$103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="52" t="inlineStr">
+        <is>
+          <t>無槓桿自由現金流（UFCF）— 預測期（人民幣百萬元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="58" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B27" s="58" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="D27" s="58" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="E27" s="58" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="F27" s="58" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B28" s="59" t="n">
+        <v>144100</v>
+      </c>
+      <c r="C28" s="59" t="n">
+        <v>182800</v>
+      </c>
+      <c r="D28" s="59" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E28" s="59" t="n">
+        <v>252900</v>
+      </c>
+      <c r="F28" s="59" t="n">
+        <v>281400</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>× (1 − 稅率)</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C29" s="55" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="D29" s="55" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E29" s="55" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="F29" s="55" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="n">
+        <v>125367</v>
+      </c>
+      <c r="C30" s="60" t="n">
+        <v>158122</v>
+      </c>
+      <c r="D30" s="60" t="n">
+        <v>187480</v>
+      </c>
+      <c r="E30" s="60" t="n">
+        <v>216230</v>
+      </c>
+      <c r="F30" s="60" t="n">
+        <v>239190</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>加：折舊與攤銷</t>
+        </is>
+      </c>
+      <c r="B31" s="59" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C31" s="59" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D31" s="59" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E31" s="59" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F31" s="59" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t>減：資本支出</t>
+        </is>
+      </c>
+      <c r="B32" s="59" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="C32" s="59" t="n">
+        <v>-9500</v>
+      </c>
+      <c r="D32" s="59" t="n">
+        <v>-11500</v>
+      </c>
+      <c r="E32" s="59" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="F32" s="59" t="n">
+        <v>-14000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="54" t="inlineStr">
+        <is>
+          <t>Δ NWC（平台浮存金效益）</t>
+        </is>
+      </c>
+      <c r="B33" s="59" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C33" s="59" t="n">
+        <v>16500</v>
+      </c>
+      <c r="D33" s="59" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E33" s="59" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F33" s="59" t="n">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="53" t="inlineStr">
+        <is>
+          <t>無槓桿自由現金流（UFCF）</t>
+        </is>
+      </c>
+      <c r="B34" s="60" t="n">
+        <v>137967</v>
+      </c>
+      <c r="C34" s="60" t="n">
+        <v>167722</v>
+      </c>
+      <c r="D34" s="60" t="n">
+        <v>194680</v>
+      </c>
+      <c r="E34" s="60" t="n">
+        <v>220530</v>
+      </c>
+      <c r="F34" s="60" t="n">
+        <v>241090</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="54" t="inlineStr">
+        <is>
+          <t>UFCF 利潤率 %</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="C35" s="55" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="D35" s="55" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="E35" s="55" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="F35" s="55" t="n">
+        <v>0.2885</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="52" t="inlineStr">
+        <is>
+          <t>現金流現值計算（基本情境：WACC = 11.5%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="58" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B39" s="58" t="inlineStr">
+        <is>
+          <t>UFCF（RMB M）</t>
+        </is>
+      </c>
+      <c r="C39" s="58" t="inlineStr">
+        <is>
+          <t>折現因子</t>
+        </is>
+      </c>
+      <c r="D39" s="58" t="inlineStr">
+        <is>
+          <t>UFCF 現值（RMB M）</t>
+        </is>
+      </c>
+      <c r="E39" s="58" t="inlineStr"/>
+      <c r="F39" s="58" t="inlineStr"/>
+      <c r="G39" s="58" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>137967</v>
+      </c>
+      <c r="C40" s="61" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="D40" s="59" t="n">
+        <v>123724</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="59" t="n">
+        <v>167722</v>
+      </c>
+      <c r="C41" s="61" t="n">
+        <v>0.8044</v>
+      </c>
+      <c r="D41" s="59" t="n">
+        <v>134930</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B42" s="59" t="n">
+        <v>194680</v>
+      </c>
+      <c r="C42" s="61" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="D42" s="59" t="n">
+        <v>140399</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B43" s="59" t="n">
+        <v>220530</v>
+      </c>
+      <c r="C43" s="61" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="D43" s="59" t="n">
+        <v>142683</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B44" s="59" t="n">
+        <v>241090</v>
+      </c>
+      <c r="C44" s="61" t="n">
+        <v>0.5803</v>
+      </c>
+      <c r="D44" s="59" t="n">
+        <v>139857</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>預測期 FCF 現值合計</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="n">
+        <v>681593</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="53" t="inlineStr">
+        <is>
+          <t>終值現值（¥241,090×1.03/(11.5%−3%) ÷ 1.115^5）</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="n">
+        <v>1695191</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="53" t="inlineStr">
+        <is>
+          <t>企業價值（EV，RMB M）</t>
+        </is>
+      </c>
+      <c r="D47" s="62" t="n">
+        <v>2376784</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A16:G16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>PDD Holdings — DCF 敏感度分析（每 ADS 股價，美元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>敏感度表1：WACC × 終值成長率 g → 每 ADS 公允價值（美元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>WACC \ g</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>g=1.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>g=2.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="64" t="inlineStr">
+        <is>
+          <t>g=2.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="64" t="inlineStr">
+        <is>
+          <t>g=3.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="64" t="inlineStr">
+        <is>
+          <t>g=3.5%</t>
+        </is>
+      </c>
+      <c r="G4" s="64" t="inlineStr">
+        <is>
+          <t>g=4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="n">
+        <v>315</v>
+      </c>
+      <c r="C5" s="65" t="n">
+        <v>330</v>
+      </c>
+      <c r="D5" s="65" t="n">
+        <v>348</v>
+      </c>
+      <c r="E5" s="65" t="n">
+        <v>369</v>
+      </c>
+      <c r="F5" s="65" t="n">
+        <v>394</v>
+      </c>
+      <c r="G5" s="65" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="n">
+        <v>281</v>
+      </c>
+      <c r="C6" s="65" t="n">
+        <v>292</v>
+      </c>
+      <c r="D6" s="65" t="n">
+        <v>306</v>
+      </c>
+      <c r="E6" s="65" t="n">
+        <v>321</v>
+      </c>
+      <c r="F6" s="65" t="n">
+        <v>338</v>
+      </c>
+      <c r="G6" s="65" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="B7" s="65" t="n">
+        <v>267</v>
+      </c>
+      <c r="C7" s="65" t="n">
+        <v>277</v>
+      </c>
+      <c r="D7" s="65" t="n">
+        <v>288</v>
+      </c>
+      <c r="E7" s="65" t="n">
+        <v>301</v>
+      </c>
+      <c r="F7" s="65" t="n">
+        <v>316</v>
+      </c>
+      <c r="G7" s="65" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="n">
+        <v>254</v>
+      </c>
+      <c r="C8" s="65" t="n">
+        <v>263</v>
+      </c>
+      <c r="D8" s="65" t="n">
+        <v>273</v>
+      </c>
+      <c r="E8" s="65" t="n">
+        <v>284</v>
+      </c>
+      <c r="F8" s="65" t="n">
+        <v>297</v>
+      </c>
+      <c r="G8" s="65" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="n">
+        <v>243</v>
+      </c>
+      <c r="C9" s="65" t="n">
+        <v>251</v>
+      </c>
+      <c r="D9" s="65" t="n">
+        <v>259</v>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>269</v>
+      </c>
+      <c r="F9" s="65" t="n">
+        <v>280</v>
+      </c>
+      <c r="G9" s="65" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="58" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="B10" s="66" t="n">
+        <v>233</v>
+      </c>
+      <c r="C10" s="66" t="n">
+        <v>240</v>
+      </c>
+      <c r="D10" s="66" t="n">
+        <v>247</v>
+      </c>
+      <c r="E10" s="65" t="n">
+        <v>256</v>
+      </c>
+      <c r="F10" s="65" t="n">
+        <v>265</v>
+      </c>
+      <c r="G10" s="65" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="B11" s="66" t="n">
+        <v>215</v>
+      </c>
+      <c r="C11" s="66" t="n">
+        <v>220</v>
+      </c>
+      <c r="D11" s="66" t="n">
+        <v>227</v>
+      </c>
+      <c r="E11" s="66" t="n">
+        <v>233</v>
+      </c>
+      <c r="F11" s="66" t="n">
+        <v>241</v>
+      </c>
+      <c r="G11" s="66" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="B12" s="66" t="n">
+        <v>200</v>
+      </c>
+      <c r="C12" s="66" t="n">
+        <v>204</v>
+      </c>
+      <c r="D12" s="66" t="n">
+        <v>209</v>
+      </c>
+      <c r="E12" s="66" t="n">
+        <v>215</v>
+      </c>
+      <c r="F12" s="66" t="n">
+        <v>221</v>
+      </c>
+      <c r="G12" s="66" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="n">
+        <v>187</v>
+      </c>
+      <c r="C13" s="66" t="n">
+        <v>191</v>
+      </c>
+      <c r="D13" s="66" t="n">
+        <v>195</v>
+      </c>
+      <c r="E13" s="66" t="n">
+        <v>199</v>
+      </c>
+      <c r="F13" s="66" t="n">
+        <v>204</v>
+      </c>
+      <c r="G13" s="66" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>敏感度表2：WACC × 收入CAGR → 每 ADS 公允價值（美元，基本情境 g=3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>WACC \ Rev CAGR</t>
+        </is>
+      </c>
+      <c r="B17" s="69" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C17" s="69" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D17" s="69" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="F17" s="69" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G17" s="69" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="H17" s="69" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="70" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="n">
+        <v>318</v>
+      </c>
+      <c r="C18" s="65" t="n">
+        <v>342</v>
+      </c>
+      <c r="D18" s="65" t="n">
+        <v>367</v>
+      </c>
+      <c r="E18" s="65" t="n">
+        <v>394</v>
+      </c>
+      <c r="F18" s="65" t="n">
+        <v>423</v>
+      </c>
+      <c r="G18" s="65" t="n">
+        <v>454</v>
+      </c>
+      <c r="H18" s="65" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="n">
+        <v>277</v>
+      </c>
+      <c r="C19" s="65" t="n">
+        <v>297</v>
+      </c>
+      <c r="D19" s="65" t="n">
+        <v>319</v>
+      </c>
+      <c r="E19" s="65" t="n">
+        <v>341</v>
+      </c>
+      <c r="F19" s="65" t="n">
+        <v>366</v>
+      </c>
+      <c r="G19" s="65" t="n">
+        <v>392</v>
+      </c>
+      <c r="H19" s="65" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="70" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="n">
+        <v>261</v>
+      </c>
+      <c r="C20" s="65" t="n">
+        <v>280</v>
+      </c>
+      <c r="D20" s="65" t="n">
+        <v>299</v>
+      </c>
+      <c r="E20" s="65" t="n">
+        <v>320</v>
+      </c>
+      <c r="F20" s="65" t="n">
+        <v>343</v>
+      </c>
+      <c r="G20" s="65" t="n">
+        <v>367</v>
+      </c>
+      <c r="H20" s="65" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="B21" s="65" t="n">
+        <v>247</v>
+      </c>
+      <c r="C21" s="65" t="n">
+        <v>264</v>
+      </c>
+      <c r="D21" s="65" t="n">
+        <v>282</v>
+      </c>
+      <c r="E21" s="65" t="n">
+        <v>302</v>
+      </c>
+      <c r="F21" s="65" t="n">
+        <v>323</v>
+      </c>
+      <c r="G21" s="65" t="n">
+        <v>345</v>
+      </c>
+      <c r="H21" s="65" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="B22" s="65" t="n">
+        <v>235</v>
+      </c>
+      <c r="C22" s="65" t="n">
+        <v>251</v>
+      </c>
+      <c r="D22" s="65" t="n">
+        <v>268</v>
+      </c>
+      <c r="E22" s="65" t="n">
+        <v>286</v>
+      </c>
+      <c r="F22" s="65" t="n">
+        <v>305</v>
+      </c>
+      <c r="G22" s="67" t="n">
+        <v>326</v>
+      </c>
+      <c r="H22" s="65" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="n">
+        <v>224</v>
+      </c>
+      <c r="C23" s="65" t="n">
+        <v>238</v>
+      </c>
+      <c r="D23" s="65" t="n">
+        <v>254</v>
+      </c>
+      <c r="E23" s="65" t="n">
+        <v>271</v>
+      </c>
+      <c r="F23" s="65" t="n">
+        <v>290</v>
+      </c>
+      <c r="G23" s="65" t="n">
+        <v>309</v>
+      </c>
+      <c r="H23" s="65" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="70" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="n">
+        <v>205</v>
+      </c>
+      <c r="C24" s="65" t="n">
+        <v>218</v>
+      </c>
+      <c r="D24" s="65" t="n">
+        <v>232</v>
+      </c>
+      <c r="E24" s="65" t="n">
+        <v>247</v>
+      </c>
+      <c r="F24" s="65" t="n">
+        <v>263</v>
+      </c>
+      <c r="G24" s="65" t="n">
+        <v>280</v>
+      </c>
+      <c r="H24" s="65" t="n">
+        <v>298</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>